--- a/docs/PD_DPDP_Compliance_Tracker_v1.0.xlsx
+++ b/docs/PD_DPDP_Compliance_Tracker_v1.0.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="126">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="142">
   <si>
     <t>PulseDesk — DPDP Compliance Tracker</t>
   </si>
@@ -329,6 +329,54 @@
   </si>
   <si>
     <t>Manual coordinates remove even that</t>
+  </si>
+  <si>
+    <t>DP-13</t>
+  </si>
+  <si>
+    <t>§4, §8 Usage analytics</t>
+  </si>
+  <si>
+    <t>Ensure any usage measurement is lawful, minimal and secured</t>
+  </si>
+  <si>
+    <t>The counter stores only a client-generated random id, date, event kind, platform and two-letter country in Cloudflare D1; no IP, cookie, email or account exists. Rows are deleted after 90 days. Evidence: worker/schema.sql, worker/src/index.js, PD-DRP-001 §2</t>
+  </si>
+  <si>
+    <t>Purpose is limited to counting devices and app opens</t>
+  </si>
+  <si>
+    <t>DP-14</t>
+  </si>
+  <si>
+    <t>§5 Notice for analytics</t>
+  </si>
+  <si>
+    <t>Tell users what is measured</t>
+  </si>
+  <si>
+    <t>The private stats page and PD-DRP-001 state it; an in-app privacy line on the web build is still to be added</t>
+  </si>
+  <si>
+    <t>2026-10-01</t>
+  </si>
+  <si>
+    <t>Tracked alongside RSK-017</t>
+  </si>
+  <si>
+    <t>DP-15</t>
+  </si>
+  <si>
+    <t>§8(7) Erasure of web data</t>
+  </si>
+  <si>
+    <t>Allow erasure of data held in the browser</t>
+  </si>
+  <si>
+    <t>Clearing site data for the domain removes holdings, settings, history and the visitor id; the visitor id is then regenerated as a new anonymous value</t>
+  </si>
+  <si>
+    <t>No server-side copy exists to erase</t>
   </si>
   <si>
     <t>CI-01</t>
@@ -1030,7 +1078,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:I19"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1432,10 +1480,10 @@
         <v>107</v>
       </c>
       <c r="D14" s="8" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E14" s="8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F14" s="8" t="s">
         <v>108</v>
@@ -1461,10 +1509,10 @@
         <v>112</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>113</v>
@@ -1473,39 +1521,126 @@
         <v>42</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>37</v>
+        <v>117</v>
       </c>
       <c r="C16" s="8" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>25</v>
       </c>
       <c r="E16" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="F16" s="8" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>117</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>42</v>
-      </c>
-      <c r="H16" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>119</v>
+      <c r="F17" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="8" t="s">
+        <v>126</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>129</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -1526,15 +1661,15 @@
   <sheetData>
     <row r="1" spans="1:2" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
       <c r="B2" s="5">
         <f>COUNTA('DPDP Tracker'!A2:A200)</f>
@@ -1558,7 +1693,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B5" s="5">
         <f>COUNTIF('DPDP Tracker'!E2:E200,"Not Started")</f>
@@ -1566,7 +1701,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
       <c r="B6" s="5">
         <f>COUNTIF('DPDP Tracker'!D2:D200,"Applicable")</f>
@@ -1574,7 +1709,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
       <c r="B7" s="5">
         <f>ROUND(COUNTIF('DPDP Tracker'!E2:E200,"Done")/COUNTA('DPDP Tracker'!A2:A200)*100,1)</f>
